--- a/서버정보/20261015_리소스배포_랜딩.xlsx
+++ b/서버정보/20261015_리소스배포_랜딩.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\zenithn\PowerShell - 리소스 배포\서버정보\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{25163CC6-61A2-4238-A56D-EFE954796CA0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{15B22C8B-E098-40F5-9598-F73DB72269BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="VM" sheetId="1" r:id="rId1"/>
@@ -1636,7 +1636,7 @@
 </file>
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
   <metadataTypes count="1">
     <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
   </metadataTypes>
@@ -1658,7 +1658,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1039" uniqueCount="250">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1045" uniqueCount="265">
   <si>
     <t>Stage</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -2525,10 +2525,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>TEMP</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>az-grayzone-host1</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -2565,26 +2561,10 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>hazr-l-sec-docams01</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>hazr-l-sec-docsol01</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>hazr-l-sec-docsol02</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>D8s_v5</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>D16ls_v5</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>10.155.194.31</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -2593,30 +2573,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>10.155.194.42</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>l-sec-docams01-disk01</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>hazr-l-sec-docsol01-disk01</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>hazr-l-sec-docsol01-disk02</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>hazr-l-sec-docsol02-disk01</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>hazr-l-sec-docsol02-disk02</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>hazr-l-mon-rg</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -2629,6 +2585,102 @@
   </si>
   <si>
     <t>10.155.161.70</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>D8ls_v5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SEC</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10.155.194.51</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>hazr-l-sec-docdb-lb</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>lsecdocams01-disk01</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>lsecdocap01-disk01</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>lsecdocdb01-disk01</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>lsecdocdb02-disk01</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>lsecdocams01-nic</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>lsecdocap01-nic</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>lsecdocdb01-nic</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>lsecdocdb02-nic</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>lsecdocams01-nsg</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>lsecdocap01-nsg</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>lsecdocdb01-nsg</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>lsecdocdb02-nsg</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>HAZRLSECDOCAP01</t>
+  </si>
+  <si>
+    <t>HAZRLSECDOCDB01</t>
+  </si>
+  <si>
+    <t>HAZRLSECDOCAMS01</t>
+  </si>
+  <si>
+    <t>HAZRLSECDOCDB02</t>
+  </si>
+  <si>
+    <t>HAZRLLSECDOCAMS01</t>
+  </si>
+  <si>
+    <t>HAZRLLSECDOCAP01</t>
+  </si>
+  <si>
+    <t>HAZRLLSECDOCDB01</t>
+  </si>
+  <si>
+    <t>HAZRLLSECDOCDB02</t>
+  </si>
+  <si>
+    <t>10.155.194.52</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10.155.194.50</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -2636,7 +2688,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="14" x14ac:knownFonts="1">
+  <fonts count="15" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2746,6 +2798,14 @@
       <b/>
       <sz val="10"/>
       <color rgb="FFFFFF00"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF00B050"/>
       <name val="맑은 고딕"/>
       <family val="2"/>
       <charset val="129"/>
@@ -3118,7 +3178,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="106">
+  <cellXfs count="110">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -3431,17 +3491,66 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="33">
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
     <dxf>
       <font>
         <strike val="0"/>
@@ -3844,43 +3953,6 @@
         <charset val="129"/>
         <scheme val="minor"/>
       </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0">
         <left style="thin">
@@ -4625,8 +4697,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="표1" displayName="표1" ref="B1:AF21" totalsRowShown="0" headerRowDxfId="32" dataDxfId="31">
-  <autoFilter ref="B1:AF21" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="표1" displayName="표1" ref="B1:AF22" totalsRowShown="0" headerRowDxfId="32" dataDxfId="31">
+  <autoFilter ref="B1:AF22" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <tableColumns count="31">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Stage" dataDxfId="30"/>
     <tableColumn id="2" xr3:uid="{DD2076C4-D866-4329-BEA8-1D816DAF3627}" name="Role" dataDxfId="29">
@@ -4651,20 +4723,20 @@
     <tableColumn id="24" xr3:uid="{00000000-0010-0000-0000-000018000000}" name="DataDiskName" dataDxfId="14"/>
     <tableColumn id="25" xr3:uid="{00000000-0010-0000-0000-000019000000}" name="DataDiskSize" dataDxfId="13"/>
     <tableColumn id="26" xr3:uid="{00000000-0010-0000-0000-00001A000000}" name="DataDiskStorageType" dataDxfId="12"/>
-    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0000-00000F000000}" name="NicName" dataDxfId="11">
-      <calculatedColumnFormula>SUBSTITUTE(F2,"hazr-","")&amp;"-nic"</calculatedColumnFormula>
+    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0000-00000F000000}" name="NicName" dataDxfId="0">
+      <calculatedColumnFormula>LOWER(SUBSTITUTE(F2,"hazr-","")&amp;"-nic")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="27" xr3:uid="{6FD9A0A6-7008-49AB-B2C9-4BEDF1811434}" name="EnableAcceleratedNetworking" dataDxfId="10"/>
-    <tableColumn id="17" xr3:uid="{00000000-0010-0000-0000-000011000000}" name="IsStatic" dataDxfId="9"/>
-    <tableColumn id="11" xr3:uid="{65903CF2-1AF4-4B86-A9E4-474DE495E3CB}" name="VnetRG" dataDxfId="8"/>
-    <tableColumn id="18" xr3:uid="{00000000-0010-0000-0000-000012000000}" name="VnetName" dataDxfId="7"/>
-    <tableColumn id="19" xr3:uid="{00000000-0010-0000-0000-000013000000}" name="SubnetName" dataDxfId="6"/>
-    <tableColumn id="28" xr3:uid="{73185387-6B41-497F-9EB6-5675CC43B3E3}" name="UseOsDiskDoubleEncryption " dataDxfId="5"/>
-    <tableColumn id="21" xr3:uid="{804782E7-599A-496A-B10D-EFCB52F3E7DB}" name="DESRG" dataDxfId="4"/>
-    <tableColumn id="16" xr3:uid="{1ED2A695-2028-4644-8B0B-7B32A8F548C4}" name="DESName" dataDxfId="3"/>
-    <tableColumn id="36" xr3:uid="{9EB3DACA-84E4-4D05-8E76-433A4A9E33E7}" name="Zones" dataDxfId="2"/>
-    <tableColumn id="20" xr3:uid="{00000000-0010-0000-0000-000014000000}" name="SubscriptionName" dataDxfId="1"/>
-    <tableColumn id="35" xr3:uid="{A2E4758D-942B-4C99-96CE-9F1494B6961B}" name="Description" dataDxfId="0"/>
+    <tableColumn id="27" xr3:uid="{6FD9A0A6-7008-49AB-B2C9-4BEDF1811434}" name="EnableAcceleratedNetworking" dataDxfId="11"/>
+    <tableColumn id="17" xr3:uid="{00000000-0010-0000-0000-000011000000}" name="IsStatic" dataDxfId="10"/>
+    <tableColumn id="11" xr3:uid="{65903CF2-1AF4-4B86-A9E4-474DE495E3CB}" name="VnetRG" dataDxfId="9"/>
+    <tableColumn id="18" xr3:uid="{00000000-0010-0000-0000-000012000000}" name="VnetName" dataDxfId="8"/>
+    <tableColumn id="19" xr3:uid="{00000000-0010-0000-0000-000013000000}" name="SubnetName" dataDxfId="7"/>
+    <tableColumn id="28" xr3:uid="{73185387-6B41-497F-9EB6-5675CC43B3E3}" name="UseOsDiskDoubleEncryption " dataDxfId="6"/>
+    <tableColumn id="21" xr3:uid="{804782E7-599A-496A-B10D-EFCB52F3E7DB}" name="DESRG" dataDxfId="5"/>
+    <tableColumn id="16" xr3:uid="{1ED2A695-2028-4644-8B0B-7B32A8F548C4}" name="DESName" dataDxfId="4"/>
+    <tableColumn id="36" xr3:uid="{9EB3DACA-84E4-4D05-8E76-433A4A9E33E7}" name="Zones" dataDxfId="3"/>
+    <tableColumn id="20" xr3:uid="{00000000-0010-0000-0000-000014000000}" name="SubscriptionName" dataDxfId="2"/>
+    <tableColumn id="35" xr3:uid="{A2E4758D-942B-4C99-96CE-9F1494B6961B}" name="Description" dataDxfId="1"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -4970,7 +5042,7 @@
   <sheetPr>
     <tabColor theme="4"/>
   </sheetPr>
-  <dimension ref="A1:AF21"/>
+  <dimension ref="A1:AF22"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="1.25" customWidth="1"/>
@@ -5157,7 +5229,7 @@
       <c r="S2" s="68"/>
       <c r="T2" s="68"/>
       <c r="U2" s="68" t="str">
-        <f t="shared" ref="U2:U3" si="1">SUBSTITUTE(F2,"hazr-","")&amp;"-nic"</f>
+        <f t="shared" ref="U2:U18" si="1">LOWER(SUBSTITUTE(F2,"hazr-","")&amp;"-nic")</f>
         <v>l-mon-whtap01-nic</v>
       </c>
       <c r="V2" s="68" t="b">
@@ -5335,7 +5407,7 @@
       <c r="S4" s="68"/>
       <c r="T4" s="68"/>
       <c r="U4" s="68" t="str">
-        <f t="shared" ref="U4:U5" si="3">SUBSTITUTE(F4,"hazr-","")&amp;"-nic"</f>
+        <f t="shared" si="1"/>
         <v>l-com-build01-nic</v>
       </c>
       <c r="V4" s="68" t="b">
@@ -5424,7 +5496,7 @@
       <c r="S5" s="68"/>
       <c r="T5" s="68"/>
       <c r="U5" s="68" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>l-com-repoweb01-nic</v>
       </c>
       <c r="V5" s="68" t="b">
@@ -5500,7 +5572,7 @@
         <v>169</v>
       </c>
       <c r="O6" s="95" t="str">
-        <f t="shared" ref="O6:O14" si="4">SUBSTITUTE(F6,"hazr-","")&amp;"-osdisk"</f>
+        <f t="shared" ref="O6:O14" si="3">SUBSTITUTE(F6,"hazr-","")&amp;"-osdisk"</f>
         <v>l-sec-virsol01-osdisk</v>
       </c>
       <c r="P6" s="96">
@@ -5513,7 +5585,7 @@
       <c r="S6" s="87"/>
       <c r="T6" s="87"/>
       <c r="U6" s="87" t="str">
-        <f t="shared" ref="U6:U14" si="5">SUBSTITUTE(F6,"hazr-","")&amp;"-nic"</f>
+        <f t="shared" si="1"/>
         <v>l-sec-virsol01-nic</v>
       </c>
       <c r="V6" s="87" t="b">
@@ -5547,7 +5619,7 @@
       <c r="AF6" s="87"/>
     </row>
     <row r="7" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A7" s="83"/>
+      <c r="A7" s="105"/>
       <c r="B7" s="87" t="s">
         <v>194</v>
       </c>
@@ -5589,7 +5661,7 @@
         <v>174</v>
       </c>
       <c r="O7" s="95" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>l-sec-wbdsol01-osdisk</v>
       </c>
       <c r="P7" s="96">
@@ -5602,7 +5674,7 @@
       <c r="S7" s="87"/>
       <c r="T7" s="87"/>
       <c r="U7" s="87" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="1"/>
         <v>l-sec-wbdsol01-nic</v>
       </c>
       <c r="V7" s="87" t="b">
@@ -5678,7 +5750,7 @@
         <v>178</v>
       </c>
       <c r="O8" s="95" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>l-com-scmsol01-osdisk</v>
       </c>
       <c r="P8" s="96">
@@ -5691,7 +5763,7 @@
       <c r="S8" s="87"/>
       <c r="T8" s="87"/>
       <c r="U8" s="87" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="1"/>
         <v>l-com-scmsol01-nic</v>
       </c>
       <c r="V8" s="87" t="b">
@@ -5767,7 +5839,7 @@
         <v>203</v>
       </c>
       <c r="O9" s="95" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>l-if-hipsproxy01-osdisk</v>
       </c>
       <c r="P9" s="96">
@@ -5780,7 +5852,7 @@
       <c r="S9" s="87"/>
       <c r="T9" s="87"/>
       <c r="U9" s="87" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="1"/>
         <v>l-if-hipsproxy01-nic</v>
       </c>
       <c r="V9" s="87" t="b">
@@ -5856,7 +5928,7 @@
         <v>209</v>
       </c>
       <c r="O10" s="95" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>l-if-sastsol01-osdisk</v>
       </c>
       <c r="P10" s="96">
@@ -5869,7 +5941,7 @@
       <c r="S10" s="87"/>
       <c r="T10" s="87"/>
       <c r="U10" s="87" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="1"/>
         <v>l-if-sastsol01-nic</v>
       </c>
       <c r="V10" s="87" t="b">
@@ -5907,7 +5979,9 @@
       <c r="B11" s="87" t="s">
         <v>194</v>
       </c>
-      <c r="C11" s="87"/>
+      <c r="C11" s="87" t="s">
+        <v>213</v>
+      </c>
       <c r="D11" s="87" t="s">
         <v>144</v>
       </c>
@@ -5939,10 +6013,10 @@
         <v>173</v>
       </c>
       <c r="N11" s="1" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="O11" s="95" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>az-erdirect-host1-osdisk</v>
       </c>
       <c r="P11" s="96">
@@ -5955,7 +6029,7 @@
       <c r="S11" s="87"/>
       <c r="T11" s="87"/>
       <c r="U11" s="87" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="1"/>
         <v>az-erdirect-host1-nic</v>
       </c>
       <c r="V11" s="87" t="b">
@@ -6027,10 +6101,10 @@
         <v>173</v>
       </c>
       <c r="N12" s="1" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="O12" s="95" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>az-erdirect-host2-osdisk</v>
       </c>
       <c r="P12" s="96">
@@ -6043,7 +6117,7 @@
       <c r="S12" s="87"/>
       <c r="T12" s="87"/>
       <c r="U12" s="87" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="1"/>
         <v>az-erdirect-host2-nic</v>
       </c>
       <c r="V12" s="87" t="b">
@@ -6115,10 +6189,10 @@
         <v>173</v>
       </c>
       <c r="N13" s="1" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="O13" s="95" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>az-erdirect-host3-osdisk</v>
       </c>
       <c r="P13" s="96">
@@ -6131,7 +6205,7 @@
       <c r="S13" s="87"/>
       <c r="T13" s="87"/>
       <c r="U13" s="87" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="1"/>
         <v>az-erdirect-host3-nic</v>
       </c>
       <c r="V13" s="87" t="b">
@@ -6203,10 +6277,10 @@
         <v>173</v>
       </c>
       <c r="N14" s="1" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="O14" s="95" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>az-erdirect-host4-osdisk</v>
       </c>
       <c r="P14" s="96">
@@ -6219,7 +6293,7 @@
       <c r="S14" s="87"/>
       <c r="T14" s="87"/>
       <c r="U14" s="87" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="1"/>
         <v>az-erdirect-host4-nic</v>
       </c>
       <c r="V14" s="87" t="b">
@@ -6267,10 +6341,10 @@
         <v>24</v>
       </c>
       <c r="F15" s="68" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="G15" s="68" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="H15" s="87" t="s">
         <v>202</v>
@@ -6291,10 +6365,10 @@
         <v>173</v>
       </c>
       <c r="N15" s="1" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="O15" s="103" t="str">
-        <f t="shared" ref="O15:O18" si="6">SUBSTITUTE(F15,"hazr-","")&amp;"-osdisk"</f>
+        <f t="shared" ref="O15:O18" si="4">SUBSTITUTE(F15,"hazr-","")&amp;"-osdisk"</f>
         <v>az-grayzone-host1-osdisk</v>
       </c>
       <c r="P15" s="96">
@@ -6307,7 +6381,7 @@
       <c r="S15" s="68"/>
       <c r="T15" s="68"/>
       <c r="U15" s="68" t="str">
-        <f t="shared" ref="U15:U18" si="7">SUBSTITUTE(F15,"hazr-","")&amp;"-nic"</f>
+        <f t="shared" si="1"/>
         <v>az-grayzone-host1-nic</v>
       </c>
       <c r="V15" s="87" t="b">
@@ -6355,10 +6429,10 @@
         <v>24</v>
       </c>
       <c r="F16" s="68" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="G16" s="68" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="H16" s="87" t="s">
         <v>202</v>
@@ -6379,10 +6453,10 @@
         <v>173</v>
       </c>
       <c r="N16" s="1" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="O16" s="103" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v>az-grayzone-host2-osdisk</v>
       </c>
       <c r="P16" s="96">
@@ -6395,7 +6469,7 @@
       <c r="S16" s="68"/>
       <c r="T16" s="68"/>
       <c r="U16" s="68" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="1"/>
         <v>az-grayzone-host2-nic</v>
       </c>
       <c r="V16" s="87" t="b">
@@ -6443,10 +6517,10 @@
         <v>24</v>
       </c>
       <c r="F17" s="68" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="G17" s="68" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="H17" s="87" t="s">
         <v>202</v>
@@ -6467,10 +6541,10 @@
         <v>173</v>
       </c>
       <c r="N17" s="1" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="O17" s="103" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v>az-grayzone-host3-osdisk</v>
       </c>
       <c r="P17" s="96">
@@ -6483,7 +6557,7 @@
       <c r="S17" s="68"/>
       <c r="T17" s="68"/>
       <c r="U17" s="68" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="1"/>
         <v>az-grayzone-host3-nic</v>
       </c>
       <c r="V17" s="87" t="b">
@@ -6531,10 +6605,10 @@
         <v>24</v>
       </c>
       <c r="F18" s="87" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="G18" s="87" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="H18" s="87" t="s">
         <v>202</v>
@@ -6555,10 +6629,10 @@
         <v>173</v>
       </c>
       <c r="N18" s="1" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="O18" s="95" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v>az-grayzone-host4-osdisk</v>
       </c>
       <c r="P18" s="96">
@@ -6571,7 +6645,7 @@
       <c r="S18" s="87"/>
       <c r="T18" s="87"/>
       <c r="U18" s="87" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="1"/>
         <v>az-grayzone-host4-nic</v>
       </c>
       <c r="V18" s="87" t="b">
@@ -6608,24 +6682,23 @@
       <c r="B19" s="87" t="s">
         <v>194</v>
       </c>
-      <c r="C19" s="87" t="str" cm="1">
-        <f t="array" ref="C19">UPPER(INDEX(_xlfn.TEXTSPLIT($F19, "-"), 3))</f>
-        <v>SEC</v>
-      </c>
-      <c r="D19" s="87" t="s">
+      <c r="C19" s="106" t="s">
+        <v>240</v>
+      </c>
+      <c r="D19" s="106" t="s">
         <v>181</v>
       </c>
       <c r="E19" s="87" t="s">
         <v>24</v>
       </c>
       <c r="F19" s="87" t="s">
+        <v>257</v>
+      </c>
+      <c r="G19" s="87" t="s">
         <v>233</v>
       </c>
-      <c r="G19" s="87" t="s">
-        <v>238</v>
-      </c>
       <c r="H19" s="87" t="s">
-        <v>236</v>
+        <v>232</v>
       </c>
       <c r="I19" s="87">
         <v>8</v>
@@ -6642,12 +6715,12 @@
       <c r="M19" s="87" t="s">
         <v>186</v>
       </c>
-      <c r="N19" s="94" t="s">
+      <c r="N19" s="104" t="s">
         <v>174</v>
       </c>
-      <c r="O19" s="95" t="str">
+      <c r="O19" s="107" t="str">
         <f>SUBSTITUTE(F19,"hazr-","")&amp;"-osdisk"</f>
-        <v>l-sec-docams01-osdisk</v>
+        <v>HAZRLSECDOCAMS01-osdisk</v>
       </c>
       <c r="P19" s="96">
         <v>128</v>
@@ -6655,26 +6728,25 @@
       <c r="Q19" s="97" t="s">
         <v>121</v>
       </c>
-      <c r="R19" s="87"/>
+      <c r="R19" s="106"/>
       <c r="S19" s="87"/>
-      <c r="T19" s="87"/>
-      <c r="U19" s="87" t="str">
-        <f>SUBSTITUTE(F19,"hazr-","")&amp;"-nic"</f>
-        <v>l-sec-docams01-nic</v>
+      <c r="T19" s="106"/>
+      <c r="U19" s="106" t="s">
+        <v>247</v>
       </c>
       <c r="V19" s="87" t="b">
         <v>1</v>
       </c>
-      <c r="W19" s="87" t="b">
+      <c r="W19" s="68" t="b">
         <v>1</v>
       </c>
       <c r="X19" s="87" t="s">
         <v>181</v>
       </c>
-      <c r="Y19" s="87" t="s">
+      <c r="Y19" s="68" t="s">
         <v>187</v>
       </c>
-      <c r="Z19" s="87" t="s">
+      <c r="Z19" s="68" t="s">
         <v>188</v>
       </c>
       <c r="AA19" s="87" t="b">
@@ -6696,65 +6768,65 @@
       <c r="B20" s="87" t="s">
         <v>194</v>
       </c>
-      <c r="C20" s="87" t="str" cm="1">
-        <f t="array" ref="C20">UPPER(INDEX(_xlfn.TEXTSPLIT($F20, "-"), 3))</f>
-        <v>SEC</v>
-      </c>
-      <c r="D20" s="87" t="s">
+      <c r="C20" s="106" t="s">
+        <v>240</v>
+      </c>
+      <c r="D20" s="106" t="s">
         <v>181</v>
       </c>
       <c r="E20" s="87" t="s">
         <v>24</v>
       </c>
-      <c r="F20" s="68" t="s">
+      <c r="F20" s="87" t="s">
+        <v>255</v>
+      </c>
+      <c r="G20" s="87" t="s">
         <v>234</v>
       </c>
-      <c r="G20" s="68" t="s">
+      <c r="H20" s="87" t="s">
         <v>239</v>
       </c>
-      <c r="H20" s="68" t="s">
-        <v>237</v>
-      </c>
-      <c r="I20" s="68">
+      <c r="I20" s="87">
+        <v>8</v>
+      </c>
+      <c r="J20" s="87">
         <v>16</v>
       </c>
-      <c r="J20" s="68">
-        <v>32</v>
-      </c>
-      <c r="K20" s="68" t="s">
+      <c r="K20" s="87" t="s">
         <v>122</v>
       </c>
-      <c r="L20" s="104" t="s">
+      <c r="L20" s="93" t="s">
         <v>120</v>
       </c>
-      <c r="M20" s="68" t="s">
+      <c r="M20" s="87" t="s">
         <v>186</v>
       </c>
-      <c r="N20" s="105" t="s">
+      <c r="N20" s="104" t="s">
         <v>174</v>
       </c>
-      <c r="O20" s="103" t="str">
-        <f t="shared" ref="O20:O21" si="8">SUBSTITUTE(F20,"hazr-","")&amp;"-osdisk"</f>
-        <v>l-sec-docsol01-osdisk</v>
-      </c>
-      <c r="P20" s="74">
+      <c r="O20" s="107" t="str">
+        <f>SUBSTITUTE(F20,"hazr-","")&amp;"-osdisk"</f>
+        <v>HAZRLSECDOCAP01-osdisk</v>
+      </c>
+      <c r="P20" s="96">
         <v>128</v>
       </c>
-      <c r="Q20" s="80" t="s">
+      <c r="Q20" s="97" t="s">
         <v>121</v>
       </c>
-      <c r="R20" s="68"/>
-      <c r="S20" s="68"/>
-      <c r="T20" s="68"/>
-      <c r="U20" s="68" t="str">
-        <f t="shared" ref="U20:U21" si="9">SUBSTITUTE(F20,"hazr-","")&amp;"-nic"</f>
-        <v>l-sec-docsol01-nic</v>
-      </c>
-      <c r="V20" s="68" t="b">
-        <v>1</v>
-      </c>
-      <c r="W20" s="68"/>
-      <c r="X20" s="68" t="s">
+      <c r="R20" s="106"/>
+      <c r="S20" s="87"/>
+      <c r="T20" s="106"/>
+      <c r="U20" s="106" t="s">
+        <v>248</v>
+      </c>
+      <c r="V20" s="87" t="b">
+        <v>1</v>
+      </c>
+      <c r="W20" s="87" t="b">
+        <v>1</v>
+      </c>
+      <c r="X20" s="87" t="s">
         <v>181</v>
       </c>
       <c r="Y20" s="68" t="s">
@@ -6772,77 +6844,75 @@
       <c r="AC20" s="87" t="s">
         <v>189</v>
       </c>
-      <c r="AD20" s="74">
-        <v>1</v>
-      </c>
-      <c r="AE20" s="68"/>
-      <c r="AF20" s="68"/>
+      <c r="AD20" s="96">
+        <v>1</v>
+      </c>
+      <c r="AE20" s="87"/>
+      <c r="AF20" s="87"/>
     </row>
     <row r="21" spans="1:32" x14ac:dyDescent="0.3">
       <c r="B21" s="87" t="s">
         <v>194</v>
       </c>
-      <c r="C21" s="87" t="str" cm="1">
-        <f t="array" ref="C21">UPPER(INDEX(_xlfn.TEXTSPLIT($F21, "-"), 3))</f>
-        <v>SEC</v>
-      </c>
-      <c r="D21" s="87" t="s">
+      <c r="C21" s="106" t="s">
+        <v>240</v>
+      </c>
+      <c r="D21" s="106" t="s">
         <v>181</v>
       </c>
       <c r="E21" s="87" t="s">
         <v>24</v>
       </c>
-      <c r="F21" s="68" t="s">
-        <v>235</v>
-      </c>
-      <c r="G21" s="68" t="s">
-        <v>240</v>
-      </c>
-      <c r="H21" s="68" t="s">
-        <v>237</v>
-      </c>
-      <c r="I21" s="68">
+      <c r="F21" s="87" t="s">
+        <v>256</v>
+      </c>
+      <c r="G21" s="87" t="s">
+        <v>241</v>
+      </c>
+      <c r="H21" s="87" t="s">
+        <v>239</v>
+      </c>
+      <c r="I21" s="87">
+        <v>8</v>
+      </c>
+      <c r="J21" s="87">
         <v>16</v>
       </c>
-      <c r="J21" s="68">
-        <v>32</v>
-      </c>
-      <c r="K21" s="68" t="s">
+      <c r="K21" s="87" t="s">
         <v>122</v>
       </c>
-      <c r="L21" s="104" t="s">
+      <c r="L21" s="93" t="s">
         <v>120</v>
       </c>
-      <c r="M21" s="68" t="s">
+      <c r="M21" s="87" t="s">
         <v>186</v>
       </c>
-      <c r="N21" s="105" t="s">
+      <c r="N21" s="104" t="s">
         <v>174</v>
       </c>
-      <c r="O21" s="103" t="str">
-        <f t="shared" si="8"/>
-        <v>l-sec-docsol02-osdisk</v>
-      </c>
-      <c r="P21" s="74">
+      <c r="O21" s="107" t="str">
+        <f>SUBSTITUTE(F21,"hazr-","")&amp;"-osdisk"</f>
+        <v>HAZRLSECDOCDB01-osdisk</v>
+      </c>
+      <c r="P21" s="96">
         <v>128</v>
       </c>
-      <c r="Q21" s="80" t="s">
+      <c r="Q21" s="97" t="s">
         <v>121</v>
       </c>
-      <c r="R21" s="68"/>
-      <c r="S21" s="68"/>
-      <c r="T21" s="68"/>
-      <c r="U21" s="68" t="str">
-        <f t="shared" si="9"/>
-        <v>l-sec-docsol02-nic</v>
-      </c>
-      <c r="V21" s="68" t="b">
-        <v>1</v>
-      </c>
-      <c r="W21" s="87" t="b">
-        <v>1</v>
-      </c>
-      <c r="X21" s="68" t="s">
+      <c r="R21" s="106"/>
+      <c r="S21" s="87"/>
+      <c r="T21" s="106"/>
+      <c r="U21" s="106" t="s">
+        <v>249</v>
+      </c>
+      <c r="V21" s="87" t="b">
+        <v>1</v>
+      </c>
+      <c r="W21" s="68" t="b">
+        <v>1</v>
+      </c>
+      <c r="X21" s="87" t="s">
         <v>181</v>
       </c>
       <c r="Y21" s="68" t="s">
@@ -6860,11 +6930,97 @@
       <c r="AC21" s="87" t="s">
         <v>189</v>
       </c>
-      <c r="AD21" s="74">
+      <c r="AD21" s="96">
+        <v>1</v>
+      </c>
+      <c r="AE21" s="87"/>
+      <c r="AF21" s="87"/>
+    </row>
+    <row r="22" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="B22" s="87" t="s">
+        <v>194</v>
+      </c>
+      <c r="C22" s="106" t="s">
+        <v>240</v>
+      </c>
+      <c r="D22" s="106" t="s">
+        <v>181</v>
+      </c>
+      <c r="E22" s="87" t="s">
+        <v>24</v>
+      </c>
+      <c r="F22" s="87" t="s">
+        <v>258</v>
+      </c>
+      <c r="G22" s="87" t="s">
+        <v>263</v>
+      </c>
+      <c r="H22" s="87" t="s">
+        <v>239</v>
+      </c>
+      <c r="I22" s="87">
+        <v>8</v>
+      </c>
+      <c r="J22" s="87">
+        <v>16</v>
+      </c>
+      <c r="K22" s="87" t="s">
+        <v>122</v>
+      </c>
+      <c r="L22" s="93" t="s">
+        <v>120</v>
+      </c>
+      <c r="M22" s="87" t="s">
+        <v>186</v>
+      </c>
+      <c r="N22" s="104" t="s">
+        <v>174</v>
+      </c>
+      <c r="O22" s="107" t="str">
+        <f>SUBSTITUTE(F22,"hazr-","")&amp;"-osdisk"</f>
+        <v>HAZRLSECDOCDB02-osdisk</v>
+      </c>
+      <c r="P22" s="96">
+        <v>128</v>
+      </c>
+      <c r="Q22" s="97" t="s">
+        <v>121</v>
+      </c>
+      <c r="R22" s="106"/>
+      <c r="S22" s="87"/>
+      <c r="T22" s="106"/>
+      <c r="U22" s="106" t="s">
+        <v>250</v>
+      </c>
+      <c r="V22" s="87" t="b">
+        <v>1</v>
+      </c>
+      <c r="W22" s="87" t="b">
+        <v>1</v>
+      </c>
+      <c r="X22" s="87" t="s">
+        <v>181</v>
+      </c>
+      <c r="Y22" s="68" t="s">
+        <v>187</v>
+      </c>
+      <c r="Z22" s="68" t="s">
+        <v>188</v>
+      </c>
+      <c r="AA22" s="87" t="b">
+        <v>1</v>
+      </c>
+      <c r="AB22" s="87" t="s">
+        <v>181</v>
+      </c>
+      <c r="AC22" s="87" t="s">
+        <v>189</v>
+      </c>
+      <c r="AD22" s="96">
         <v>2</v>
       </c>
-      <c r="AE21" s="68"/>
-      <c r="AF21" s="68"/>
+      <c r="AE22" s="87"/>
+      <c r="AF22" s="87"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -6881,7 +7037,7 @@
   <sheetPr>
     <tabColor theme="4"/>
   </sheetPr>
-  <dimension ref="A1:R13"/>
+  <dimension ref="A1:R14"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="1.25" style="69" customWidth="1"/>
@@ -7434,154 +7590,184 @@
       <c r="R10" s="68"/>
     </row>
     <row r="11" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="B11" s="100" t="s">
+      <c r="B11" s="68" t="s">
         <v>194</v>
       </c>
-      <c r="C11" s="100" t="str" cm="1">
-        <f t="array" ref="C11">UPPER(INDEX(_xlfn.TEXTSPLIT($F11, "-"), 3))</f>
-        <v>SEC</v>
-      </c>
-      <c r="D11" s="100" t="s">
+      <c r="C11" s="68" t="s">
+        <v>240</v>
+      </c>
+      <c r="D11" s="68" t="s">
         <v>181</v>
       </c>
-      <c r="E11" s="100" t="s">
+      <c r="E11" s="68" t="s">
         <v>24</v>
       </c>
-      <c r="F11" s="100" t="s">
-        <v>233</v>
-      </c>
-      <c r="G11" s="100" t="s">
-        <v>241</v>
-      </c>
-      <c r="H11" s="100" t="s">
+      <c r="F11" s="68" t="s">
+        <v>259</v>
+      </c>
+      <c r="G11" s="68" t="s">
+        <v>243</v>
+      </c>
+      <c r="H11" s="68" t="s">
         <v>121</v>
       </c>
-      <c r="I11" s="100">
+      <c r="I11" s="68">
         <v>2048</v>
       </c>
-      <c r="J11" s="100"/>
-      <c r="K11" s="100"/>
-      <c r="L11" s="100"/>
-      <c r="M11" s="100">
-        <v>1</v>
-      </c>
-      <c r="N11" s="100" t="s">
+      <c r="J11" s="68"/>
+      <c r="K11" s="68"/>
+      <c r="L11" s="68"/>
+      <c r="M11" s="68">
+        <v>1</v>
+      </c>
+      <c r="N11" s="68" t="s">
         <v>133</v>
       </c>
-      <c r="O11" s="100" t="s">
+      <c r="O11" s="68" t="s">
         <v>181</v>
       </c>
-      <c r="P11" s="100" t="s">
+      <c r="P11" s="68" t="s">
         <v>189</v>
       </c>
-      <c r="Q11" s="100" t="b">
-        <v>1</v>
-      </c>
-      <c r="R11" s="100"/>
+      <c r="Q11" s="68" t="b">
+        <v>1</v>
+      </c>
+      <c r="R11" s="68"/>
     </row>
     <row r="12" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="B12" s="68" t="s">
+      <c r="B12" s="100" t="s">
         <v>194</v>
       </c>
-      <c r="C12" s="68" t="str" cm="1">
-        <f t="array" ref="C12">UPPER(INDEX(_xlfn.TEXTSPLIT($F12, "-"), 3))</f>
-        <v>SEC</v>
-      </c>
-      <c r="D12" s="68" t="s">
+      <c r="C12" s="100" t="s">
+        <v>240</v>
+      </c>
+      <c r="D12" s="100" t="s">
         <v>181</v>
       </c>
-      <c r="E12" s="68" t="s">
+      <c r="E12" s="100" t="s">
         <v>24</v>
       </c>
-      <c r="F12" s="68" t="s">
-        <v>234</v>
-      </c>
-      <c r="G12" s="68" t="s">
-        <v>242</v>
-      </c>
-      <c r="H12" s="68" t="s">
+      <c r="F12" s="100" t="s">
+        <v>260</v>
+      </c>
+      <c r="G12" s="100" t="s">
+        <v>244</v>
+      </c>
+      <c r="H12" s="100" t="s">
         <v>121</v>
       </c>
-      <c r="I12" s="68">
+      <c r="I12" s="100">
+        <v>1024</v>
+      </c>
+      <c r="J12" s="100"/>
+      <c r="K12" s="100"/>
+      <c r="L12" s="100"/>
+      <c r="M12" s="100">
+        <v>1</v>
+      </c>
+      <c r="N12" s="100" t="s">
+        <v>133</v>
+      </c>
+      <c r="O12" s="100" t="s">
+        <v>181</v>
+      </c>
+      <c r="P12" s="100" t="s">
+        <v>189</v>
+      </c>
+      <c r="Q12" s="100" t="b">
+        <v>1</v>
+      </c>
+      <c r="R12" s="100"/>
+    </row>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="B13" s="68" t="s">
+        <v>194</v>
+      </c>
+      <c r="C13" s="68" t="s">
+        <v>240</v>
+      </c>
+      <c r="D13" s="68" t="s">
+        <v>181</v>
+      </c>
+      <c r="E13" s="68" t="s">
+        <v>24</v>
+      </c>
+      <c r="F13" s="68" t="s">
+        <v>261</v>
+      </c>
+      <c r="G13" s="68" t="s">
+        <v>245</v>
+      </c>
+      <c r="H13" s="68" t="s">
+        <v>121</v>
+      </c>
+      <c r="I13" s="68">
         <v>2048</v>
       </c>
-      <c r="J12" s="68" t="s">
-        <v>243</v>
-      </c>
-      <c r="K12" s="68" t="s">
+      <c r="J13" s="68"/>
+      <c r="K13" s="68"/>
+      <c r="L13" s="68"/>
+      <c r="M13" s="68">
+        <v>1</v>
+      </c>
+      <c r="N13" s="68" t="s">
+        <v>133</v>
+      </c>
+      <c r="O13" s="68" t="s">
+        <v>181</v>
+      </c>
+      <c r="P13" s="68" t="s">
+        <v>189</v>
+      </c>
+      <c r="Q13" s="68" t="b">
+        <v>1</v>
+      </c>
+      <c r="R13" s="68"/>
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="B14" s="100" t="s">
+        <v>194</v>
+      </c>
+      <c r="C14" s="100" t="s">
+        <v>240</v>
+      </c>
+      <c r="D14" s="100" t="s">
+        <v>181</v>
+      </c>
+      <c r="E14" s="100" t="s">
+        <v>24</v>
+      </c>
+      <c r="F14" s="100" t="s">
+        <v>262</v>
+      </c>
+      <c r="G14" s="100" t="s">
+        <v>246</v>
+      </c>
+      <c r="H14" s="100" t="s">
         <v>121</v>
       </c>
-      <c r="L12" s="68">
-        <v>1024</v>
-      </c>
-      <c r="M12" s="68">
-        <v>1</v>
-      </c>
-      <c r="N12" s="68" t="s">
+      <c r="I14" s="100">
+        <v>2048</v>
+      </c>
+      <c r="J14" s="100"/>
+      <c r="K14" s="100"/>
+      <c r="L14" s="100"/>
+      <c r="M14" s="100">
+        <v>2</v>
+      </c>
+      <c r="N14" s="100" t="s">
         <v>133</v>
       </c>
-      <c r="O12" s="68" t="s">
+      <c r="O14" s="100" t="s">
         <v>181</v>
       </c>
-      <c r="P12" s="68" t="s">
+      <c r="P14" s="100" t="s">
         <v>189</v>
       </c>
-      <c r="Q12" s="68" t="b">
-        <v>1</v>
-      </c>
-      <c r="R12" s="68"/>
-    </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="B13" s="100" t="s">
-        <v>194</v>
-      </c>
-      <c r="C13" s="100" t="str" cm="1">
-        <f t="array" ref="C13">UPPER(INDEX(_xlfn.TEXTSPLIT($F13, "-"), 3))</f>
-        <v>SEC</v>
-      </c>
-      <c r="D13" s="100" t="s">
-        <v>181</v>
-      </c>
-      <c r="E13" s="100" t="s">
-        <v>24</v>
-      </c>
-      <c r="F13" s="100" t="s">
-        <v>235</v>
-      </c>
-      <c r="G13" s="100" t="s">
-        <v>244</v>
-      </c>
-      <c r="H13" s="100" t="s">
-        <v>121</v>
-      </c>
-      <c r="I13" s="100">
-        <v>2048</v>
-      </c>
-      <c r="J13" s="100" t="s">
-        <v>245</v>
-      </c>
-      <c r="K13" s="100" t="s">
-        <v>121</v>
-      </c>
-      <c r="L13" s="100">
-        <v>1024</v>
-      </c>
-      <c r="M13" s="100">
-        <v>2</v>
-      </c>
-      <c r="N13" s="100" t="s">
-        <v>133</v>
-      </c>
-      <c r="O13" s="100" t="s">
-        <v>181</v>
-      </c>
-      <c r="P13" s="100" t="s">
-        <v>189</v>
-      </c>
-      <c r="Q13" s="100" t="b">
-        <v>1</v>
-      </c>
-      <c r="R13" s="100"/>
+      <c r="Q14" s="100" t="b">
+        <v>1</v>
+      </c>
+      <c r="R14" s="100"/>
     </row>
   </sheetData>
   <autoFilter ref="B1:R8" xr:uid="{52F281E7-0665-4BB7-80DB-4208A01A998B}"/>
@@ -8784,7 +8970,7 @@
   <sheetPr>
     <tabColor theme="4"/>
   </sheetPr>
-  <dimension ref="A1:M21"/>
+  <dimension ref="A1:M14"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="1.5" customWidth="1"/>
@@ -8795,7 +8981,7 @@
     <col min="7" max="7" width="16.875" style="69" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="18.5" style="69" bestFit="1" customWidth="1"/>
     <col min="9" max="10" width="18.5" style="69" customWidth="1"/>
-    <col min="11" max="11" width="18" style="69" customWidth="1"/>
+    <col min="11" max="11" width="21.75" style="69" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="9" style="69"/>
   </cols>
   <sheetData>
@@ -9189,7 +9375,7 @@
         <v>144</v>
       </c>
       <c r="K10" s="74" t="str">
-        <f t="shared" ref="K10:K11" si="7">SUBSTITUTE(I10,"hazr-","")&amp;"-nic"</f>
+        <f t="shared" ref="K10" si="7">SUBSTITUTE(I10,"hazr-","")&amp;"-nic"</f>
         <v>l-if-sastsol01-nic</v>
       </c>
       <c r="L10" s="74" t="s">
@@ -9202,33 +9388,31 @@
         <v>194</v>
       </c>
       <c r="C11" s="72" t="s">
-        <v>223</v>
+        <v>240</v>
       </c>
       <c r="D11" s="72" t="s">
-        <v>144</v>
-      </c>
-      <c r="E11" s="72" t="str">
-        <f t="shared" ref="E11:E21" si="8">SUBSTITUTE(I11,"hazr-","")&amp;"-nsg"</f>
-        <v>az-erdirect-host1-nsg</v>
+        <v>181</v>
+      </c>
+      <c r="E11" s="72" t="s">
+        <v>251</v>
       </c>
       <c r="F11" s="72" t="s">
-        <v>144</v>
+        <v>181</v>
       </c>
       <c r="G11" s="72" t="s">
-        <v>138</v>
+        <v>187</v>
       </c>
       <c r="H11" s="72" t="s">
-        <v>222</v>
-      </c>
-      <c r="I11" s="99" t="s">
-        <v>214</v>
+        <v>188</v>
+      </c>
+      <c r="I11" s="72" t="s">
+        <v>257</v>
       </c>
       <c r="J11" s="72" t="s">
-        <v>144</v>
-      </c>
-      <c r="K11" s="72" t="str">
-        <f t="shared" si="7"/>
-        <v>az-erdirect-host1-nic</v>
+        <v>181</v>
+      </c>
+      <c r="K11" s="108" t="s">
+        <v>247</v>
       </c>
       <c r="L11" s="72" t="s">
         <v>140</v>
@@ -9240,33 +9424,31 @@
         <v>194</v>
       </c>
       <c r="C12" s="74" t="s">
-        <v>223</v>
+        <v>240</v>
       </c>
       <c r="D12" s="74" t="s">
-        <v>144</v>
-      </c>
-      <c r="E12" s="74" t="str">
-        <f t="shared" si="8"/>
-        <v>az-erdirect-host2-nsg</v>
+        <v>181</v>
+      </c>
+      <c r="E12" s="74" t="s">
+        <v>252</v>
       </c>
       <c r="F12" s="74" t="s">
-        <v>144</v>
+        <v>181</v>
       </c>
       <c r="G12" s="74" t="s">
-        <v>138</v>
+        <v>187</v>
       </c>
       <c r="H12" s="74" t="s">
-        <v>222</v>
-      </c>
-      <c r="I12" s="98" t="s">
-        <v>216</v>
+        <v>188</v>
+      </c>
+      <c r="I12" s="74" t="s">
+        <v>255</v>
       </c>
       <c r="J12" s="74" t="s">
-        <v>144</v>
-      </c>
-      <c r="K12" s="74" t="str">
-        <f t="shared" ref="K12:K15" si="9">SUBSTITUTE(I12,"hazr-","")&amp;"-nic"</f>
-        <v>az-erdirect-host2-nic</v>
+        <v>181</v>
+      </c>
+      <c r="K12" s="109" t="s">
+        <v>248</v>
       </c>
       <c r="L12" s="74" t="s">
         <v>140</v>
@@ -9278,33 +9460,31 @@
         <v>194</v>
       </c>
       <c r="C13" s="72" t="s">
-        <v>223</v>
+        <v>240</v>
       </c>
       <c r="D13" s="72" t="s">
-        <v>144</v>
-      </c>
-      <c r="E13" s="72" t="str">
-        <f t="shared" si="8"/>
-        <v>az-erdirect-host3-nsg</v>
+        <v>181</v>
+      </c>
+      <c r="E13" s="72" t="s">
+        <v>253</v>
       </c>
       <c r="F13" s="72" t="s">
-        <v>144</v>
+        <v>181</v>
       </c>
       <c r="G13" s="72" t="s">
-        <v>138</v>
+        <v>187</v>
       </c>
       <c r="H13" s="72" t="s">
-        <v>222</v>
-      </c>
-      <c r="I13" s="99" t="s">
-        <v>215</v>
+        <v>188</v>
+      </c>
+      <c r="I13" s="72" t="s">
+        <v>256</v>
       </c>
       <c r="J13" s="72" t="s">
-        <v>144</v>
-      </c>
-      <c r="K13" s="72" t="str">
-        <f t="shared" si="9"/>
-        <v>az-erdirect-host3-nic</v>
+        <v>181</v>
+      </c>
+      <c r="K13" s="108" t="s">
+        <v>249</v>
       </c>
       <c r="L13" s="72" t="s">
         <v>140</v>
@@ -9316,307 +9496,36 @@
         <v>194</v>
       </c>
       <c r="C14" s="74" t="s">
-        <v>223</v>
+        <v>240</v>
       </c>
       <c r="D14" s="74" t="s">
-        <v>144</v>
-      </c>
-      <c r="E14" s="74" t="str">
-        <f t="shared" si="8"/>
-        <v>az-erdirect-host4-nsg</v>
+        <v>181</v>
+      </c>
+      <c r="E14" s="74" t="s">
+        <v>254</v>
       </c>
       <c r="F14" s="74" t="s">
-        <v>144</v>
+        <v>181</v>
       </c>
       <c r="G14" s="74" t="s">
-        <v>138</v>
+        <v>187</v>
       </c>
       <c r="H14" s="74" t="s">
-        <v>222</v>
-      </c>
-      <c r="I14" s="98" t="s">
-        <v>217</v>
+        <v>188</v>
+      </c>
+      <c r="I14" s="74" t="s">
+        <v>258</v>
       </c>
       <c r="J14" s="74" t="s">
-        <v>144</v>
-      </c>
-      <c r="K14" s="74" t="str">
-        <f t="shared" si="9"/>
-        <v>az-erdirect-host4-nic</v>
+        <v>181</v>
+      </c>
+      <c r="K14" s="109" t="s">
+        <v>250</v>
       </c>
       <c r="L14" s="74" t="s">
         <v>140</v>
       </c>
       <c r="M14" s="74"/>
-    </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="B15" s="72" t="s">
-        <v>194</v>
-      </c>
-      <c r="C15" s="72" t="s">
-        <v>213</v>
-      </c>
-      <c r="D15" s="72" t="s">
-        <v>144</v>
-      </c>
-      <c r="E15" s="72" t="str">
-        <f t="shared" si="8"/>
-        <v>az-grayzone-host1-nsg</v>
-      </c>
-      <c r="F15" s="72" t="s">
-        <v>144</v>
-      </c>
-      <c r="G15" s="72" t="s">
-        <v>138</v>
-      </c>
-      <c r="H15" s="72" t="s">
-        <v>171</v>
-      </c>
-      <c r="I15" s="67" t="s">
-        <v>224</v>
-      </c>
-      <c r="J15" s="72" t="s">
-        <v>144</v>
-      </c>
-      <c r="K15" s="72" t="str">
-        <f t="shared" si="9"/>
-        <v>az-grayzone-host1-nic</v>
-      </c>
-      <c r="L15" s="72" t="s">
-        <v>140</v>
-      </c>
-      <c r="M15" s="72"/>
-    </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="B16" s="74" t="s">
-        <v>194</v>
-      </c>
-      <c r="C16" s="74" t="s">
-        <v>213</v>
-      </c>
-      <c r="D16" s="74" t="s">
-        <v>144</v>
-      </c>
-      <c r="E16" s="74" t="str">
-        <f t="shared" si="8"/>
-        <v>az-grayzone-host2-nsg</v>
-      </c>
-      <c r="F16" s="74" t="s">
-        <v>144</v>
-      </c>
-      <c r="G16" s="74" t="s">
-        <v>138</v>
-      </c>
-      <c r="H16" s="74" t="s">
-        <v>171</v>
-      </c>
-      <c r="I16" s="68" t="s">
-        <v>225</v>
-      </c>
-      <c r="J16" s="74" t="s">
-        <v>144</v>
-      </c>
-      <c r="K16" s="74" t="str">
-        <f t="shared" ref="K16:K21" si="10">SUBSTITUTE(I16,"hazr-","")&amp;"-nic"</f>
-        <v>az-grayzone-host2-nic</v>
-      </c>
-      <c r="L16" s="74" t="s">
-        <v>140</v>
-      </c>
-      <c r="M16" s="74"/>
-    </row>
-    <row r="17" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="B17" s="72" t="s">
-        <v>194</v>
-      </c>
-      <c r="C17" s="72" t="s">
-        <v>213</v>
-      </c>
-      <c r="D17" s="72" t="s">
-        <v>144</v>
-      </c>
-      <c r="E17" s="72" t="str">
-        <f t="shared" si="8"/>
-        <v>az-grayzone-host3-nsg</v>
-      </c>
-      <c r="F17" s="72" t="s">
-        <v>144</v>
-      </c>
-      <c r="G17" s="72" t="s">
-        <v>138</v>
-      </c>
-      <c r="H17" s="72" t="s">
-        <v>171</v>
-      </c>
-      <c r="I17" s="67" t="s">
-        <v>226</v>
-      </c>
-      <c r="J17" s="72" t="s">
-        <v>144</v>
-      </c>
-      <c r="K17" s="72" t="str">
-        <f t="shared" si="10"/>
-        <v>az-grayzone-host3-nic</v>
-      </c>
-      <c r="L17" s="72" t="s">
-        <v>140</v>
-      </c>
-      <c r="M17" s="72"/>
-    </row>
-    <row r="18" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="B18" s="74" t="s">
-        <v>194</v>
-      </c>
-      <c r="C18" s="74" t="s">
-        <v>213</v>
-      </c>
-      <c r="D18" s="74" t="s">
-        <v>144</v>
-      </c>
-      <c r="E18" s="74" t="str">
-        <f t="shared" si="8"/>
-        <v>az-grayzone-host4-nsg</v>
-      </c>
-      <c r="F18" s="74" t="s">
-        <v>144</v>
-      </c>
-      <c r="G18" s="74" t="s">
-        <v>138</v>
-      </c>
-      <c r="H18" s="74" t="s">
-        <v>171</v>
-      </c>
-      <c r="I18" s="98" t="s">
-        <v>227</v>
-      </c>
-      <c r="J18" s="74" t="s">
-        <v>144</v>
-      </c>
-      <c r="K18" s="74" t="str">
-        <f t="shared" si="10"/>
-        <v>az-grayzone-host4-nic</v>
-      </c>
-      <c r="L18" s="74" t="s">
-        <v>140</v>
-      </c>
-      <c r="M18" s="74"/>
-    </row>
-    <row r="19" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="B19" s="72" t="s">
-        <v>194</v>
-      </c>
-      <c r="C19" s="72" t="str" cm="1">
-        <f t="array" ref="C19">UPPER(INDEX(_xlfn.TEXTSPLIT($E19, "-"), 2))</f>
-        <v>SEC</v>
-      </c>
-      <c r="D19" s="72" t="s">
-        <v>181</v>
-      </c>
-      <c r="E19" s="72" t="str">
-        <f t="shared" si="8"/>
-        <v>l-sec-docams01-nsg</v>
-      </c>
-      <c r="F19" s="72" t="s">
-        <v>181</v>
-      </c>
-      <c r="G19" s="72" t="s">
-        <v>187</v>
-      </c>
-      <c r="H19" s="72" t="s">
-        <v>188</v>
-      </c>
-      <c r="I19" s="72" t="s">
-        <v>233</v>
-      </c>
-      <c r="J19" s="72" t="s">
-        <v>181</v>
-      </c>
-      <c r="K19" s="72" t="str">
-        <f t="shared" si="10"/>
-        <v>l-sec-docams01-nic</v>
-      </c>
-      <c r="L19" s="72" t="s">
-        <v>140</v>
-      </c>
-      <c r="M19" s="72"/>
-    </row>
-    <row r="20" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="B20" s="74" t="s">
-        <v>194</v>
-      </c>
-      <c r="C20" s="74" t="str" cm="1">
-        <f t="array" ref="C20">UPPER(INDEX(_xlfn.TEXTSPLIT($E20, "-"), 2))</f>
-        <v>SEC</v>
-      </c>
-      <c r="D20" s="74" t="s">
-        <v>181</v>
-      </c>
-      <c r="E20" s="74" t="str">
-        <f t="shared" si="8"/>
-        <v>l-sec-docsol01-nsg</v>
-      </c>
-      <c r="F20" s="74" t="s">
-        <v>181</v>
-      </c>
-      <c r="G20" s="74" t="s">
-        <v>187</v>
-      </c>
-      <c r="H20" s="74" t="s">
-        <v>188</v>
-      </c>
-      <c r="I20" s="74" t="s">
-        <v>234</v>
-      </c>
-      <c r="J20" s="74" t="s">
-        <v>181</v>
-      </c>
-      <c r="K20" s="74" t="str">
-        <f t="shared" si="10"/>
-        <v>l-sec-docsol01-nic</v>
-      </c>
-      <c r="L20" s="74" t="s">
-        <v>140</v>
-      </c>
-      <c r="M20" s="74"/>
-    </row>
-    <row r="21" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="B21" s="72" t="s">
-        <v>194</v>
-      </c>
-      <c r="C21" s="72" t="str" cm="1">
-        <f t="array" ref="C21">UPPER(INDEX(_xlfn.TEXTSPLIT($E21, "-"), 2))</f>
-        <v>SEC</v>
-      </c>
-      <c r="D21" s="72" t="s">
-        <v>181</v>
-      </c>
-      <c r="E21" s="72" t="str">
-        <f t="shared" si="8"/>
-        <v>l-sec-docsol02-nsg</v>
-      </c>
-      <c r="F21" s="72" t="s">
-        <v>181</v>
-      </c>
-      <c r="G21" s="72" t="s">
-        <v>187</v>
-      </c>
-      <c r="H21" s="72" t="s">
-        <v>188</v>
-      </c>
-      <c r="I21" s="72" t="s">
-        <v>235</v>
-      </c>
-      <c r="J21" s="72" t="s">
-        <v>181</v>
-      </c>
-      <c r="K21" s="72" t="str">
-        <f t="shared" si="10"/>
-        <v>l-sec-docsol02-nic</v>
-      </c>
-      <c r="L21" s="72" t="s">
-        <v>140</v>
-      </c>
-      <c r="M21" s="72"/>
     </row>
   </sheetData>
   <autoFilter ref="B1:M8" xr:uid="{BAB1F184-7BFC-47CB-AC71-63C76B7E3D12}"/>
@@ -9715,13 +9624,13 @@
         <v>MON</v>
       </c>
       <c r="D2" s="76" t="s">
-        <v>246</v>
+        <v>235</v>
       </c>
       <c r="E2" s="76" t="s">
         <v>24</v>
       </c>
       <c r="F2" s="76" t="s">
-        <v>248</v>
+        <v>237</v>
       </c>
       <c r="G2" s="76" t="s">
         <v>101</v>
@@ -9736,7 +9645,7 @@
         <v>92</v>
       </c>
       <c r="K2" s="76" t="str">
-        <f t="shared" ref="K2:K31" si="0">SUBSTITUTE(F2, "hazr-", "")&amp;"-fe"</f>
+        <f t="shared" ref="K2:K3" si="0">SUBSTITUTE(F2, "hazr-", "")&amp;"-fe"</f>
         <v>l-mon-whtap-lb-fe</v>
       </c>
       <c r="L2" s="76" t="s">
@@ -9752,7 +9661,7 @@
         <v>98</v>
       </c>
       <c r="P2" s="76" t="s">
-        <v>249</v>
+        <v>238</v>
       </c>
       <c r="Q2" s="77" t="str">
         <f>SUBSTITUTE(F2, "hazr-", "")&amp;"-bp"</f>
@@ -9761,22 +9670,56 @@
     </row>
     <row r="3" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A3" s="83"/>
-      <c r="B3" s="68"/>
-      <c r="C3" s="68"/>
-      <c r="D3" s="68"/>
-      <c r="E3" s="68"/>
-      <c r="F3" s="68"/>
-      <c r="G3" s="68"/>
-      <c r="H3" s="68"/>
-      <c r="I3" s="68"/>
-      <c r="J3" s="68"/>
-      <c r="K3" s="68"/>
-      <c r="L3" s="68"/>
-      <c r="M3" s="68"/>
-      <c r="N3" s="68"/>
-      <c r="O3" s="68"/>
-      <c r="P3" s="68"/>
-      <c r="Q3" s="78"/>
+      <c r="B3" s="68" t="s">
+        <v>194</v>
+      </c>
+      <c r="C3" s="68" t="s">
+        <v>240</v>
+      </c>
+      <c r="D3" s="68" t="s">
+        <v>181</v>
+      </c>
+      <c r="E3" s="68" t="s">
+        <v>24</v>
+      </c>
+      <c r="F3" s="68" t="s">
+        <v>242</v>
+      </c>
+      <c r="G3" s="68" t="s">
+        <v>101</v>
+      </c>
+      <c r="H3" s="68" t="s">
+        <v>180</v>
+      </c>
+      <c r="I3" s="68" t="s">
+        <v>179</v>
+      </c>
+      <c r="J3" s="68" t="s">
+        <v>92</v>
+      </c>
+      <c r="K3" s="68" t="str">
+        <f t="shared" si="0"/>
+        <v>l-sec-docdb-lb-fe</v>
+      </c>
+      <c r="L3" s="68" t="s">
+        <v>181</v>
+      </c>
+      <c r="M3" s="68" t="s">
+        <v>187</v>
+      </c>
+      <c r="N3" s="68" t="s">
+        <v>188</v>
+      </c>
+      <c r="O3" s="68" t="s">
+        <v>98</v>
+      </c>
+      <c r="P3" s="68" t="s">
+        <v>264</v>
+      </c>
+      <c r="Q3" s="68" t="str">
+        <f>SUBSTITUTE(F3, "hazr-", "")&amp;"-bp"</f>
+        <v>l-sec-docdb-lb-bp</v>
+      </c>
     </row>
     <row r="4" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A4" s="83"/>
@@ -10548,7 +10491,7 @@
   <sheetPr>
     <tabColor rgb="FFFFFF00"/>
   </sheetPr>
-  <dimension ref="A1:K2"/>
+  <dimension ref="A1:K3"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="2.375" customWidth="1"/>
@@ -10602,10 +10545,10 @@
         <v>MON</v>
       </c>
       <c r="D2" s="76" t="s">
-        <v>246</v>
+        <v>235</v>
       </c>
       <c r="E2" s="76" t="s">
-        <v>248</v>
+        <v>237</v>
       </c>
       <c r="F2" s="48" t="str">
         <f t="shared" ref="F2" si="0">SUBSTITUTE(E2, "hazr-", "")&amp;"-pb"&amp;H2</f>
@@ -10622,6 +10565,38 @@
         <v>5</v>
       </c>
       <c r="K2" s="76">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="B3" s="68" t="s">
+        <v>194</v>
+      </c>
+      <c r="C3" s="68" t="str" cm="1">
+        <f t="array" ref="C3">UPPER(INDEX(_xlfn.TEXTSPLIT($D3, "-"), 3))</f>
+        <v>SEC</v>
+      </c>
+      <c r="D3" s="68" t="s">
+        <v>181</v>
+      </c>
+      <c r="E3" s="68" t="s">
+        <v>242</v>
+      </c>
+      <c r="F3" s="68" t="str">
+        <f t="shared" ref="F3" si="1">SUBSTITUTE(E3, "hazr-", "")&amp;"-pb"&amp;H3</f>
+        <v>l-sec-docdb-lb-pb10433</v>
+      </c>
+      <c r="G3" s="68" t="s">
+        <v>57</v>
+      </c>
+      <c r="H3" s="68">
+        <v>10433</v>
+      </c>
+      <c r="I3" s="68"/>
+      <c r="J3" s="68">
+        <v>5</v>
+      </c>
+      <c r="K3" s="68">
         <v>2</v>
       </c>
     </row>
@@ -10636,7 +10611,7 @@
   <sheetPr>
     <tabColor rgb="FFFFFF00"/>
   </sheetPr>
-  <dimension ref="A1:S2"/>
+  <dimension ref="A1:S3"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="3.375" customWidth="1"/>
@@ -10722,10 +10697,10 @@
         <v>MON</v>
       </c>
       <c r="D2" s="76" t="s">
-        <v>246</v>
+        <v>235</v>
       </c>
       <c r="E2" s="76" t="s">
-        <v>247</v>
+        <v>236</v>
       </c>
       <c r="F2" s="76" t="str">
         <f t="shared" ref="F2" si="0">SUBSTITUTE(E2, "hazr-", "")&amp;"-rule"&amp;O2</f>
@@ -10771,6 +10746,67 @@
         <v>1</v>
       </c>
       <c r="S2" s="76" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="B3" s="68" t="s">
+        <v>194</v>
+      </c>
+      <c r="C3" s="68" t="str" cm="1">
+        <f t="array" ref="C3">UPPER(INDEX(_xlfn.TEXTSPLIT($D3, "-"), 3))</f>
+        <v>SEC</v>
+      </c>
+      <c r="D3" s="68" t="s">
+        <v>181</v>
+      </c>
+      <c r="E3" s="68" t="s">
+        <v>242</v>
+      </c>
+      <c r="F3" s="68" t="str">
+        <f t="shared" ref="F3" si="4">SUBSTITUTE(E3, "hazr-", "")&amp;"-rule"&amp;O3</f>
+        <v>l-sec-docdb-lb-rule10433</v>
+      </c>
+      <c r="G3" s="68" t="str">
+        <f t="shared" ref="G3" si="5">SUBSTITUTE(E3, "hazr-", "")&amp;"-fe"</f>
+        <v>l-sec-docdb-lb-fe</v>
+      </c>
+      <c r="H3" s="68" t="s">
+        <v>57</v>
+      </c>
+      <c r="I3" s="68">
+        <v>10433</v>
+      </c>
+      <c r="J3" s="68" t="b">
+        <v>0</v>
+      </c>
+      <c r="K3" s="68" t="str">
+        <f t="shared" ref="K3" si="6">SUBSTITUTE(E3, "hazr-", "")&amp;"-bp"</f>
+        <v>l-sec-docdb-lb-bp</v>
+      </c>
+      <c r="L3" s="68">
+        <v>10433</v>
+      </c>
+      <c r="M3" s="68" t="str">
+        <f t="shared" ref="M3" si="7">SUBSTITUTE(E3, "hazr-", "")&amp;"-pb"&amp;IF(O3="", "", O3)</f>
+        <v>l-sec-docdb-lb-pb10433</v>
+      </c>
+      <c r="N3" s="68" t="s">
+        <v>57</v>
+      </c>
+      <c r="O3" s="68">
+        <v>10433</v>
+      </c>
+      <c r="P3" s="68">
+        <v>4</v>
+      </c>
+      <c r="Q3" s="68" t="s">
+        <v>113</v>
+      </c>
+      <c r="R3" s="68" t="b">
+        <v>1</v>
+      </c>
+      <c r="S3" s="68" t="b">
         <v>0</v>
       </c>
     </row>
@@ -10787,9 +10823,12 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -10937,26 +10976,15 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BF093BAC-4385-48E8-8492-BA8C8E7EF612}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CAFDA824-0F2E-4C40-8FCD-BF3D34EF26B3}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="89f0f392-688b-4454-b192-0691f37dc811"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -10980,9 +11008,17 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CAFDA824-0F2E-4C40-8FCD-BF3D34EF26B3}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BF093BAC-4385-48E8-8492-BA8C8E7EF612}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="89f0f392-688b-4454-b192-0691f37dc811"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/서버정보/20261015_리소스배포_랜딩.xlsx
+++ b/서버정보/20261015_리소스배포_랜딩.xlsx
@@ -1636,7 +1636,7 @@
 </file>
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
   <metadataTypes count="1">
     <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
   </metadataTypes>
@@ -3178,7 +3178,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="110">
+  <cellXfs count="106">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -3497,60 +3497,11 @@
     <xf numFmtId="0" fontId="14" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="33">
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
     <dxf>
       <font>
         <strike val="0"/>
@@ -3953,6 +3904,43 @@
         <charset val="129"/>
         <scheme val="minor"/>
       </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0">
         <left style="thin">
@@ -4723,20 +4711,20 @@
     <tableColumn id="24" xr3:uid="{00000000-0010-0000-0000-000018000000}" name="DataDiskName" dataDxfId="14"/>
     <tableColumn id="25" xr3:uid="{00000000-0010-0000-0000-000019000000}" name="DataDiskSize" dataDxfId="13"/>
     <tableColumn id="26" xr3:uid="{00000000-0010-0000-0000-00001A000000}" name="DataDiskStorageType" dataDxfId="12"/>
-    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0000-00000F000000}" name="NicName" dataDxfId="0">
+    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0000-00000F000000}" name="NicName" dataDxfId="11">
       <calculatedColumnFormula>LOWER(SUBSTITUTE(F2,"hazr-","")&amp;"-nic")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="27" xr3:uid="{6FD9A0A6-7008-49AB-B2C9-4BEDF1811434}" name="EnableAcceleratedNetworking" dataDxfId="11"/>
-    <tableColumn id="17" xr3:uid="{00000000-0010-0000-0000-000011000000}" name="IsStatic" dataDxfId="10"/>
-    <tableColumn id="11" xr3:uid="{65903CF2-1AF4-4B86-A9E4-474DE495E3CB}" name="VnetRG" dataDxfId="9"/>
-    <tableColumn id="18" xr3:uid="{00000000-0010-0000-0000-000012000000}" name="VnetName" dataDxfId="8"/>
-    <tableColumn id="19" xr3:uid="{00000000-0010-0000-0000-000013000000}" name="SubnetName" dataDxfId="7"/>
-    <tableColumn id="28" xr3:uid="{73185387-6B41-497F-9EB6-5675CC43B3E3}" name="UseOsDiskDoubleEncryption " dataDxfId="6"/>
-    <tableColumn id="21" xr3:uid="{804782E7-599A-496A-B10D-EFCB52F3E7DB}" name="DESRG" dataDxfId="5"/>
-    <tableColumn id="16" xr3:uid="{1ED2A695-2028-4644-8B0B-7B32A8F548C4}" name="DESName" dataDxfId="4"/>
-    <tableColumn id="36" xr3:uid="{9EB3DACA-84E4-4D05-8E76-433A4A9E33E7}" name="Zones" dataDxfId="3"/>
-    <tableColumn id="20" xr3:uid="{00000000-0010-0000-0000-000014000000}" name="SubscriptionName" dataDxfId="2"/>
-    <tableColumn id="35" xr3:uid="{A2E4758D-942B-4C99-96CE-9F1494B6961B}" name="Description" dataDxfId="1"/>
+    <tableColumn id="27" xr3:uid="{6FD9A0A6-7008-49AB-B2C9-4BEDF1811434}" name="EnableAcceleratedNetworking" dataDxfId="10"/>
+    <tableColumn id="17" xr3:uid="{00000000-0010-0000-0000-000011000000}" name="IsStatic" dataDxfId="9"/>
+    <tableColumn id="11" xr3:uid="{65903CF2-1AF4-4B86-A9E4-474DE495E3CB}" name="VnetRG" dataDxfId="8"/>
+    <tableColumn id="18" xr3:uid="{00000000-0010-0000-0000-000012000000}" name="VnetName" dataDxfId="7"/>
+    <tableColumn id="19" xr3:uid="{00000000-0010-0000-0000-000013000000}" name="SubnetName" dataDxfId="6"/>
+    <tableColumn id="28" xr3:uid="{73185387-6B41-497F-9EB6-5675CC43B3E3}" name="UseOsDiskDoubleEncryption " dataDxfId="5"/>
+    <tableColumn id="21" xr3:uid="{804782E7-599A-496A-B10D-EFCB52F3E7DB}" name="DESRG" dataDxfId="4"/>
+    <tableColumn id="16" xr3:uid="{1ED2A695-2028-4644-8B0B-7B32A8F548C4}" name="DESName" dataDxfId="3"/>
+    <tableColumn id="36" xr3:uid="{9EB3DACA-84E4-4D05-8E76-433A4A9E33E7}" name="Zones" dataDxfId="2"/>
+    <tableColumn id="20" xr3:uid="{00000000-0010-0000-0000-000014000000}" name="SubscriptionName" dataDxfId="1"/>
+    <tableColumn id="35" xr3:uid="{A2E4758D-942B-4C99-96CE-9F1494B6961B}" name="Description" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -6682,10 +6670,10 @@
       <c r="B19" s="87" t="s">
         <v>194</v>
       </c>
-      <c r="C19" s="106" t="s">
+      <c r="C19" s="87" t="s">
         <v>240</v>
       </c>
-      <c r="D19" s="106" t="s">
+      <c r="D19" s="87" t="s">
         <v>181</v>
       </c>
       <c r="E19" s="87" t="s">
@@ -6718,7 +6706,7 @@
       <c r="N19" s="104" t="s">
         <v>174</v>
       </c>
-      <c r="O19" s="107" t="str">
+      <c r="O19" s="95" t="str">
         <f>SUBSTITUTE(F19,"hazr-","")&amp;"-osdisk"</f>
         <v>HAZRLSECDOCAMS01-osdisk</v>
       </c>
@@ -6728,10 +6716,10 @@
       <c r="Q19" s="97" t="s">
         <v>121</v>
       </c>
-      <c r="R19" s="106"/>
+      <c r="R19" s="87"/>
       <c r="S19" s="87"/>
-      <c r="T19" s="106"/>
-      <c r="U19" s="106" t="s">
+      <c r="T19" s="87"/>
+      <c r="U19" s="87" t="s">
         <v>247</v>
       </c>
       <c r="V19" s="87" t="b">
@@ -6768,10 +6756,10 @@
       <c r="B20" s="87" t="s">
         <v>194</v>
       </c>
-      <c r="C20" s="106" t="s">
+      <c r="C20" s="87" t="s">
         <v>240</v>
       </c>
-      <c r="D20" s="106" t="s">
+      <c r="D20" s="87" t="s">
         <v>181</v>
       </c>
       <c r="E20" s="87" t="s">
@@ -6804,7 +6792,7 @@
       <c r="N20" s="104" t="s">
         <v>174</v>
       </c>
-      <c r="O20" s="107" t="str">
+      <c r="O20" s="95" t="str">
         <f>SUBSTITUTE(F20,"hazr-","")&amp;"-osdisk"</f>
         <v>HAZRLSECDOCAP01-osdisk</v>
       </c>
@@ -6814,10 +6802,10 @@
       <c r="Q20" s="97" t="s">
         <v>121</v>
       </c>
-      <c r="R20" s="106"/>
+      <c r="R20" s="87"/>
       <c r="S20" s="87"/>
-      <c r="T20" s="106"/>
-      <c r="U20" s="106" t="s">
+      <c r="T20" s="87"/>
+      <c r="U20" s="87" t="s">
         <v>248</v>
       </c>
       <c r="V20" s="87" t="b">
@@ -6854,10 +6842,10 @@
       <c r="B21" s="87" t="s">
         <v>194</v>
       </c>
-      <c r="C21" s="106" t="s">
+      <c r="C21" s="87" t="s">
         <v>240</v>
       </c>
-      <c r="D21" s="106" t="s">
+      <c r="D21" s="87" t="s">
         <v>181</v>
       </c>
       <c r="E21" s="87" t="s">
@@ -6890,7 +6878,7 @@
       <c r="N21" s="104" t="s">
         <v>174</v>
       </c>
-      <c r="O21" s="107" t="str">
+      <c r="O21" s="95" t="str">
         <f>SUBSTITUTE(F21,"hazr-","")&amp;"-osdisk"</f>
         <v>HAZRLSECDOCDB01-osdisk</v>
       </c>
@@ -6900,10 +6888,10 @@
       <c r="Q21" s="97" t="s">
         <v>121</v>
       </c>
-      <c r="R21" s="106"/>
+      <c r="R21" s="87"/>
       <c r="S21" s="87"/>
-      <c r="T21" s="106"/>
-      <c r="U21" s="106" t="s">
+      <c r="T21" s="87"/>
+      <c r="U21" s="87" t="s">
         <v>249</v>
       </c>
       <c r="V21" s="87" t="b">
@@ -6940,10 +6928,10 @@
       <c r="B22" s="87" t="s">
         <v>194</v>
       </c>
-      <c r="C22" s="106" t="s">
+      <c r="C22" s="87" t="s">
         <v>240</v>
       </c>
-      <c r="D22" s="106" t="s">
+      <c r="D22" s="87" t="s">
         <v>181</v>
       </c>
       <c r="E22" s="87" t="s">
@@ -6976,7 +6964,7 @@
       <c r="N22" s="104" t="s">
         <v>174</v>
       </c>
-      <c r="O22" s="107" t="str">
+      <c r="O22" s="95" t="str">
         <f>SUBSTITUTE(F22,"hazr-","")&amp;"-osdisk"</f>
         <v>HAZRLSECDOCDB02-osdisk</v>
       </c>
@@ -6986,10 +6974,10 @@
       <c r="Q22" s="97" t="s">
         <v>121</v>
       </c>
-      <c r="R22" s="106"/>
+      <c r="R22" s="87"/>
       <c r="S22" s="87"/>
-      <c r="T22" s="106"/>
-      <c r="U22" s="106" t="s">
+      <c r="T22" s="87"/>
+      <c r="U22" s="87" t="s">
         <v>250</v>
       </c>
       <c r="V22" s="87" t="b">
@@ -9411,7 +9399,7 @@
       <c r="J11" s="72" t="s">
         <v>181</v>
       </c>
-      <c r="K11" s="108" t="s">
+      <c r="K11" s="99" t="s">
         <v>247</v>
       </c>
       <c r="L11" s="72" t="s">
@@ -9447,7 +9435,7 @@
       <c r="J12" s="74" t="s">
         <v>181</v>
       </c>
-      <c r="K12" s="109" t="s">
+      <c r="K12" s="98" t="s">
         <v>248</v>
       </c>
       <c r="L12" s="74" t="s">
@@ -9483,7 +9471,7 @@
       <c r="J13" s="72" t="s">
         <v>181</v>
       </c>
-      <c r="K13" s="108" t="s">
+      <c r="K13" s="99" t="s">
         <v>249</v>
       </c>
       <c r="L13" s="72" t="s">
@@ -9519,7 +9507,7 @@
       <c r="J14" s="74" t="s">
         <v>181</v>
       </c>
-      <c r="K14" s="109" t="s">
+      <c r="K14" s="98" t="s">
         <v>250</v>
       </c>
       <c r="L14" s="74" t="s">
@@ -10823,12 +10811,9 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -10976,15 +10961,26 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CAFDA824-0F2E-4C40-8FCD-BF3D34EF26B3}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BF093BAC-4385-48E8-8492-BA8C8E7EF612}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="89f0f392-688b-4454-b192-0691f37dc811"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -11008,17 +11004,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BF093BAC-4385-48E8-8492-BA8C8E7EF612}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CAFDA824-0F2E-4C40-8FCD-BF3D34EF26B3}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="89f0f392-688b-4454-b192-0691f37dc811"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>